--- a/reports/service-tracking-report-KIM-LAWAN-evaluator-cache-serviceTracking-KIM-LAWAN-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-KIM-LAWAN-evaluator-cache-serviceTracking-KIM-LAWAN-XIII-202501-202612.xlsx
@@ -10,58 +10,22 @@
     <x:sheet name="February 2026" sheetId="8" r:id="rId8"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="Applicants">Sheet1!$A$6:$M$7</x:definedName>
+    <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
     <x:definedName name="summary">#REF!</x:definedName>
   </x:definedNames>
   <x:calcPr/>
   <x:extLst>
     <x:ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="M1zy22YtJ+TLWEM7ow84Ac98JQFmbAbmONakZm1eVcw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6Gqj+nP2ZfjBIlYJvjiPFyqmWD9usEriw94U1uDhyO0="/>
     </x:ext>
   </x:extLst>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <x:si>
-    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Application Type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPANY NAME / NAME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STATUS(NEW/REN/DUP)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULL ADDRESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PERMIT NO.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REFERENCE NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE OF FILING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EXPIRATION DATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OR NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMOUNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE PAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BY</x:t>
+    <x:t>{{Name}}</x:t>
   </x:si>
   <x:si>
     <x:t>Restricted Radiotelephone Operator's Certificate for Land Mobile Station (NEW)</x:t>
@@ -119,7 +83,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="11">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -146,12 +110,6 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="13.0"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
       <x:color theme="1"/>
       <x:name val="Arial"/>
     </x:font>
@@ -162,17 +120,23 @@
     </x:font>
     <x:font>
       <x:b/>
+      <x:sz val="13.0"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -180,20 +144,13 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="18"/>
       <x:color rgb="FFFFFFFF"/>
-      <x:name val="Arial"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -221,15 +178,15 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="14">
+  <x:borders count="15">
     <x:border/>
     <x:border>
-      <x:left style="thin">
-        <x:color rgb="FF000000"/>
-      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
@@ -241,14 +198,14 @@
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
@@ -266,10 +223,10 @@
       <x:right style="none">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="none">
+      <x:top style="thin">
         <x:color rgb="FF000000"/>
       </x:top>
-      <x:bottom style="none">
+      <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
       <x:diagonal style="none">
@@ -280,13 +237,30 @@
       <x:left style="none">
         <x:color rgb="FF000000"/>
       </x:left>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
+      </x:left>
       <x:right style="thick">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="none">
+      <x:top style="thin">
         <x:color rgb="FF000000"/>
       </x:top>
-      <x:bottom style="none">
+      <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
       <x:diagonal style="none">
@@ -441,37 +415,37 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="6" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -480,16 +454,13 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -498,67 +469,78 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="26">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="0" shrinkToFit="0" readingOrder="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="0" shrinkToFit="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -570,20 +552,20 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -591,6 +573,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -854,190 +840,186 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45748</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>16</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>17</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
         <x:v>45761.1071296296</x:v>
       </x:c>
-      <x:c r="I6" s="12">
+      <x:c r="I6" s="13">
         <x:v>45761.1071412037</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="n">
+      <x:c r="J6" s="12" t="n">
         <x:v>1459705</x:v>
       </x:c>
-      <x:c r="K6" s="13" t="n">
+      <x:c r="K6" s="14" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="L6" s="12">
+      <x:c r="L6" s="15">
         <x:v>45761.1243865741</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="8" t="s"/>
-      <x:c r="C7" s="8" t="s"/>
-      <x:c r="D7" s="8" t="s"/>
-      <x:c r="E7" s="8" t="s"/>
-      <x:c r="F7" s="8" t="s"/>
-      <x:c r="G7" s="8" t="s"/>
-      <x:c r="H7" s="8" t="s"/>
-      <x:c r="I7" s="8" t="s"/>
-      <x:c r="J7" s="8" t="s"/>
-      <x:c r="K7" s="8" t="s"/>
-      <x:c r="L7" s="8" t="s"/>
-      <x:c r="M7" s="8" t="s"/>
-      <x:c r="N7" s="7" t="s"/>
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="16" t="s"/>
+      <x:c r="C7" s="16" t="s"/>
+      <x:c r="D7" s="16" t="s"/>
+      <x:c r="E7" s="16" t="s"/>
+      <x:c r="F7" s="16" t="s"/>
+      <x:c r="G7" s="16" t="s"/>
+      <x:c r="H7" s="16" t="s"/>
+      <x:c r="I7" s="16" t="s"/>
+      <x:c r="J7" s="16" t="s"/>
+      <x:c r="K7" s="16" t="s"/>
+      <x:c r="L7" s="16" t="s"/>
+      <x:c r="M7" s="16" t="s"/>
+      <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="9" t="s"/>
+      <x:c r="C8" s="9" t="s"/>
+      <x:c r="D8" s="9" t="s"/>
+      <x:c r="E8" s="9" t="s"/>
+      <x:c r="F8" s="9" t="s"/>
+      <x:c r="G8" s="9" t="s"/>
+      <x:c r="H8" s="9" t="s"/>
+      <x:c r="I8" s="9" t="s"/>
+      <x:c r="J8" s="9" t="s"/>
+      <x:c r="K8" s="9" t="s"/>
+      <x:c r="L8" s="9" t="s"/>
+      <x:c r="M8" s="9" t="s"/>
+    </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C9" s="15" t="s"/>
-      <x:c r="D9" s="15" t="s"/>
-      <x:c r="E9" s="16" t="s"/>
-      <x:c r="F9" s="16" t="s"/>
+      <x:c r="B9" s="17" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C9" s="18" t="s"/>
+      <x:c r="D9" s="18" t="s"/>
+      <x:c r="E9" s="19" t="s"/>
+      <x:c r="F9" s="19" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C10" s="18" t="s"/>
-      <x:c r="D10" s="18" t="s"/>
-      <x:c r="E10" s="18" t="s"/>
-      <x:c r="F10" s="19" t="s">
-        <x:v>22</x:v>
+      <x:c r="B10" s="20" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C10" s="21" t="s"/>
+      <x:c r="D10" s="21" t="s"/>
+      <x:c r="E10" s="21" t="s"/>
+      <x:c r="F10" s="22" t="s">
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="20" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="21" t="s"/>
-      <x:c r="D11" s="21" t="s"/>
-      <x:c r="E11" s="21" t="s"/>
-      <x:c r="F11" s="22" t="n">
+      <x:c r="B11" s="23" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="24" t="s"/>
+      <x:c r="D11" s="24" t="s"/>
+      <x:c r="E11" s="24" t="s"/>
+      <x:c r="F11" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="23" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C12" s="24" t="s"/>
-      <x:c r="D12" s="24" t="s"/>
-      <x:c r="E12" s="24" t="s"/>
-      <x:c r="F12" s="25" t="n">
+      <x:c r="B12" s="26" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C12" s="27" t="s"/>
+      <x:c r="D12" s="27" t="s"/>
+      <x:c r="E12" s="27" t="s"/>
+      <x:c r="F12" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2105,188 +2087,184 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46054</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>24</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s"/>
       <x:c r="E6" s="11" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
         <x:v>46078.1190856481</x:v>
       </x:c>
-      <x:c r="I6" s="12">
+      <x:c r="I6" s="13">
         <x:v>46078.1190856481</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="n">
+      <x:c r="J6" s="12" t="n">
         <x:v>1516142</x:v>
       </x:c>
-      <x:c r="K6" s="13" t="n">
+      <x:c r="K6" s="14" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L6" s="12">
+      <x:c r="L6" s="15">
         <x:v>46078.3824768519</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="8" t="s"/>
-      <x:c r="C7" s="8" t="s"/>
-      <x:c r="D7" s="8" t="s"/>
-      <x:c r="E7" s="8" t="s"/>
-      <x:c r="F7" s="8" t="s"/>
-      <x:c r="G7" s="8" t="s"/>
-      <x:c r="H7" s="8" t="s"/>
-      <x:c r="I7" s="8" t="s"/>
-      <x:c r="J7" s="8" t="s"/>
-      <x:c r="K7" s="8" t="s"/>
-      <x:c r="L7" s="8" t="s"/>
-      <x:c r="M7" s="8" t="s"/>
-      <x:c r="N7" s="7" t="s"/>
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="16" t="s"/>
+      <x:c r="C7" s="16" t="s"/>
+      <x:c r="D7" s="16" t="s"/>
+      <x:c r="E7" s="16" t="s"/>
+      <x:c r="F7" s="16" t="s"/>
+      <x:c r="G7" s="16" t="s"/>
+      <x:c r="H7" s="16" t="s"/>
+      <x:c r="I7" s="16" t="s"/>
+      <x:c r="J7" s="16" t="s"/>
+      <x:c r="K7" s="16" t="s"/>
+      <x:c r="L7" s="16" t="s"/>
+      <x:c r="M7" s="16" t="s"/>
+      <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="9" t="s"/>
+      <x:c r="C8" s="9" t="s"/>
+      <x:c r="D8" s="9" t="s"/>
+      <x:c r="E8" s="9" t="s"/>
+      <x:c r="F8" s="9" t="s"/>
+      <x:c r="G8" s="9" t="s"/>
+      <x:c r="H8" s="9" t="s"/>
+      <x:c r="I8" s="9" t="s"/>
+      <x:c r="J8" s="9" t="s"/>
+      <x:c r="K8" s="9" t="s"/>
+      <x:c r="L8" s="9" t="s"/>
+      <x:c r="M8" s="9" t="s"/>
+    </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C9" s="15" t="s"/>
-      <x:c r="D9" s="15" t="s"/>
-      <x:c r="E9" s="16" t="s"/>
-      <x:c r="F9" s="16" t="s"/>
+      <x:c r="B9" s="17" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C9" s="18" t="s"/>
+      <x:c r="D9" s="18" t="s"/>
+      <x:c r="E9" s="19" t="s"/>
+      <x:c r="F9" s="19" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C10" s="18" t="s"/>
-      <x:c r="D10" s="18" t="s"/>
-      <x:c r="E10" s="18" t="s"/>
-      <x:c r="F10" s="19" t="s">
-        <x:v>22</x:v>
+      <x:c r="B10" s="20" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C10" s="21" t="s"/>
+      <x:c r="D10" s="21" t="s"/>
+      <x:c r="E10" s="21" t="s"/>
+      <x:c r="F10" s="22" t="s">
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="20" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C11" s="21" t="s"/>
-      <x:c r="D11" s="21" t="s"/>
-      <x:c r="E11" s="21" t="s"/>
-      <x:c r="F11" s="22" t="n">
+      <x:c r="B11" s="23" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C11" s="24" t="s"/>
+      <x:c r="D11" s="24" t="s"/>
+      <x:c r="E11" s="24" t="s"/>
+      <x:c r="F11" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="23" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C12" s="24" t="s"/>
-      <x:c r="D12" s="24" t="s"/>
-      <x:c r="E12" s="24" t="s"/>
-      <x:c r="F12" s="25" t="n">
+      <x:c r="B12" s="26" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C12" s="27" t="s"/>
+      <x:c r="D12" s="27" t="s"/>
+      <x:c r="E12" s="27" t="s"/>
+      <x:c r="F12" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-KIM-LAWAN-evaluator-cache-serviceTracking-KIM-LAWAN-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-KIM-LAWAN-evaluator-cache-serviceTracking-KIM-LAWAN-XIII-202501-202612.xlsx
@@ -23,9 +23,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <x:si>
-    <x:t>{{Name}}</x:t>
+    <x:t>EVALUATOR SUMMARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KIM LAWAN</x:t>
   </x:si>
   <x:si>
     <x:t>Restricted Radiotelephone Operator's Certificate for Land Mobile Station (NEW)</x:t>
@@ -144,7 +147,7 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="18"/>
       <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -178,7 +181,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="15">
+  <x:borders count="14">
     <x:border/>
     <x:border>
       <x:right style="thin">
@@ -223,10 +226,10 @@
       <x:right style="none">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="thin">
+      <x:top style="none">
         <x:color rgb="FF000000"/>
       </x:top>
-      <x:bottom style="thin">
+      <x:bottom style="none">
         <x:color rgb="FF000000"/>
       </x:bottom>
       <x:diagonal style="none">
@@ -237,30 +240,13 @@
       <x:left style="none">
         <x:color rgb="FF000000"/>
       </x:left>
-      <x:right style="none">
+      <x:right style="thick">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="thin">
+      <x:top style="none">
         <x:color rgb="FF000000"/>
       </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF000000"/>
-      </x:bottom>
-      <x:diagonal style="none">
-        <x:color rgb="FF000000"/>
-      </x:diagonal>
-    </x:border>
-    <x:border diagonalUp="0" diagonalDown="0">
-      <x:left style="none">
-        <x:color rgb="FF000000"/>
-      </x:left>
-      <x:right style="thick">
-        <x:color rgb="FF000000"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
-      <x:bottom style="thin">
+      <x:bottom style="none">
         <x:color rgb="FF000000"/>
       </x:bottom>
       <x:diagonal style="none">
@@ -442,10 +428,13 @@
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="6" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -454,13 +443,13 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -469,11 +458,8 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="29">
+  <x:cellXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -509,38 +495,46 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -552,11 +546,7 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -564,8 +554,12 @@
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -573,10 +567,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -825,7 +815,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -842,7 +834,7 @@
     <x:row r="3" spans="1:28">
       <x:c r="A3" s="3" t="s"/>
       <x:c r="B3" s="3">
-        <x:v>45748</x:v>
+        <x:v>46082</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s"/>
       <x:c r="D3" s="3" t="s"/>
@@ -903,24 +895,24 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D6" s="12" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H6" s="13">
         <x:v>45761.1071296296</x:v>
@@ -938,7 +930,7 @@
         <x:v>45761.1243865741</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
@@ -959,29 +951,27 @@
       <x:c r="M7" s="16" t="s"/>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s"/>
-      <x:c r="C8" s="9" t="s"/>
-      <x:c r="D8" s="9" t="s"/>
-      <x:c r="E8" s="9" t="s"/>
-      <x:c r="F8" s="9" t="s"/>
-      <x:c r="G8" s="9" t="s"/>
-      <x:c r="H8" s="9" t="s"/>
-      <x:c r="I8" s="9" t="s"/>
-      <x:c r="J8" s="9" t="s"/>
-      <x:c r="K8" s="9" t="s"/>
-      <x:c r="L8" s="9" t="s"/>
-      <x:c r="M8" s="9" t="s"/>
+      <x:c r="B8" s="17" t="s"/>
+      <x:c r="C8" s="17" t="s"/>
+      <x:c r="D8" s="17" t="s"/>
+      <x:c r="E8" s="17" t="s"/>
+      <x:c r="F8" s="17" t="s"/>
+      <x:c r="G8" s="17" t="s"/>
+      <x:c r="H8" s="17" t="s"/>
+      <x:c r="I8" s="17" t="s"/>
+      <x:c r="J8" s="17" t="s"/>
+      <x:c r="K8" s="17" t="s"/>
+      <x:c r="L8" s="17" t="s"/>
+      <x:c r="M8" s="17" t="s"/>
     </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="17" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C9" s="18" t="s"/>
-      <x:c r="D9" s="18" t="s"/>
-      <x:c r="E9" s="19" t="s"/>
-      <x:c r="F9" s="19" t="s"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
       <x:c r="G9" s="9" t="s"/>
       <x:c r="H9" s="9" t="s"/>
       <x:c r="I9" s="9" t="s"/>
@@ -990,41 +980,49 @@
       <x:c r="L9" s="9" t="s"/>
       <x:c r="M9" s="9" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="20" t="s">
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="18" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C10" s="21" t="s"/>
-      <x:c r="D10" s="21" t="s"/>
-      <x:c r="E10" s="21" t="s"/>
-      <x:c r="F10" s="22" t="s">
+      <x:c r="C11" s="19" t="s"/>
+      <x:c r="D11" s="19" t="s"/>
+      <x:c r="E11" s="20" t="s"/>
+      <x:c r="F11" s="20" t="s"/>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="21" t="s">
         <x:v>10</x:v>
       </x:c>
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="23" t="s">
+        <x:v>11</x:v>
+      </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="23" t="s">
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="24" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C11" s="24" t="s"/>
-      <x:c r="D11" s="24" t="s"/>
-      <x:c r="E11" s="24" t="s"/>
-      <x:c r="F11" s="25" t="n">
+    </x:row>
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="27" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="26" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C12" s="27" t="s"/>
-      <x:c r="D12" s="27" t="s"/>
-      <x:c r="E12" s="27" t="s"/>
-      <x:c r="F12" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2005,13 +2003,14 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="6">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B9:F9"/>
-    <x:mergeCell ref="B10:E10"/>
-    <x:mergeCell ref="B11:E11"/>
+  <x:mergeCells count="7">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -2072,7 +2071,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -2089,7 +2090,7 @@
     <x:row r="3" spans="1:28">
       <x:c r="A3" s="3" t="s"/>
       <x:c r="B3" s="3">
-        <x:v>46054</x:v>
+        <x:v>46082</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s"/>
       <x:c r="D3" s="3" t="s"/>
@@ -2150,22 +2151,22 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D6" s="12" t="s"/>
       <x:c r="E6" s="11" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H6" s="13">
         <x:v>46078.1190856481</x:v>
@@ -2183,7 +2184,7 @@
         <x:v>46078.3824768519</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
@@ -2204,29 +2205,27 @@
       <x:c r="M7" s="16" t="s"/>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s"/>
-      <x:c r="C8" s="9" t="s"/>
-      <x:c r="D8" s="9" t="s"/>
-      <x:c r="E8" s="9" t="s"/>
-      <x:c r="F8" s="9" t="s"/>
-      <x:c r="G8" s="9" t="s"/>
-      <x:c r="H8" s="9" t="s"/>
-      <x:c r="I8" s="9" t="s"/>
-      <x:c r="J8" s="9" t="s"/>
-      <x:c r="K8" s="9" t="s"/>
-      <x:c r="L8" s="9" t="s"/>
-      <x:c r="M8" s="9" t="s"/>
+      <x:c r="B8" s="17" t="s"/>
+      <x:c r="C8" s="17" t="s"/>
+      <x:c r="D8" s="17" t="s"/>
+      <x:c r="E8" s="17" t="s"/>
+      <x:c r="F8" s="17" t="s"/>
+      <x:c r="G8" s="17" t="s"/>
+      <x:c r="H8" s="17" t="s"/>
+      <x:c r="I8" s="17" t="s"/>
+      <x:c r="J8" s="17" t="s"/>
+      <x:c r="K8" s="17" t="s"/>
+      <x:c r="L8" s="17" t="s"/>
+      <x:c r="M8" s="17" t="s"/>
     </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="17" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C9" s="18" t="s"/>
-      <x:c r="D9" s="18" t="s"/>
-      <x:c r="E9" s="19" t="s"/>
-      <x:c r="F9" s="19" t="s"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
       <x:c r="G9" s="9" t="s"/>
       <x:c r="H9" s="9" t="s"/>
       <x:c r="I9" s="9" t="s"/>
@@ -2235,41 +2234,49 @@
       <x:c r="L9" s="9" t="s"/>
       <x:c r="M9" s="9" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="20" t="s">
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="18" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C10" s="21" t="s"/>
-      <x:c r="D10" s="21" t="s"/>
-      <x:c r="E10" s="21" t="s"/>
-      <x:c r="F10" s="22" t="s">
+      <x:c r="C11" s="19" t="s"/>
+      <x:c r="D11" s="19" t="s"/>
+      <x:c r="E11" s="20" t="s"/>
+      <x:c r="F11" s="20" t="s"/>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="21" t="s">
         <x:v>10</x:v>
       </x:c>
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="23" t="s">
+        <x:v>11</x:v>
+      </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="23" t="s">
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="24" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="27" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C11" s="24" t="s"/>
-      <x:c r="D11" s="24" t="s"/>
-      <x:c r="E11" s="24" t="s"/>
-      <x:c r="F11" s="25" t="n">
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="26" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C12" s="27" t="s"/>
-      <x:c r="D12" s="27" t="s"/>
-      <x:c r="E12" s="27" t="s"/>
-      <x:c r="F12" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3250,13 +3257,14 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="6">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B9:F9"/>
-    <x:mergeCell ref="B10:E10"/>
-    <x:mergeCell ref="B11:E11"/>
+  <x:mergeCells count="7">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-KIM-LAWAN-evaluator-cache-serviceTracking-KIM-LAWAN-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-KIM-LAWAN-evaluator-cache-serviceTracking-KIM-LAWAN-XIII-202501-202612.xlsx
@@ -865,7 +865,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -935,7 +935,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s"/>
       <x:c r="C7" s="16" t="s"/>
@@ -2121,7 +2121,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -2189,7 +2189,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s"/>
       <x:c r="C7" s="16" t="s"/>

--- a/reports/service-tracking-report-KIM-LAWAN-evaluator-cache-serviceTracking-KIM-LAWAN-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-KIM-LAWAN-evaluator-cache-serviceTracking-KIM-LAWAN-XIII-202501-202612.xlsx
@@ -23,12 +23,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
   <x:si>
     <x:t>KIM LAWAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Application Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPANY NAME / NAME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STATUS(NEW/REN/DUP)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULL ADDRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PERMIT NO.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REFERENCE NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE OF FILING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EXPIRATION DATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OR NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMOUNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE PAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BY</x:t>
   </x:si>
   <x:si>
     <x:t>Restricted Radiotelephone Operator's Certificate for Land Mobile Station (NEW)</x:t>
@@ -86,7 +122,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="11">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -131,15 +167,15 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -154,6 +190,13 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -401,27 +444,24 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -443,10 +483,13 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -459,7 +502,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="30">
+  <x:cellXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -490,36 +533,20 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -546,15 +573,15 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -867,18 +894,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -896,75 +911,87 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45761.1071296296</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>45761.1071412037</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1459705</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>45761.1243865741</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s"/>
-      <x:c r="C7" s="16" t="s"/>
-      <x:c r="D7" s="16" t="s"/>
-      <x:c r="E7" s="16" t="s"/>
-      <x:c r="F7" s="16" t="s"/>
-      <x:c r="G7" s="16" t="s"/>
-      <x:c r="H7" s="16" t="s"/>
-      <x:c r="I7" s="16" t="s"/>
-      <x:c r="J7" s="16" t="s"/>
-      <x:c r="K7" s="16" t="s"/>
-      <x:c r="L7" s="16" t="s"/>
-      <x:c r="M7" s="16" t="s"/>
+      <x:c r="B7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="17" t="s"/>
-      <x:c r="C8" s="17" t="s"/>
-      <x:c r="D8" s="17" t="s"/>
-      <x:c r="E8" s="17" t="s"/>
-      <x:c r="F8" s="17" t="s"/>
-      <x:c r="G8" s="17" t="s"/>
-      <x:c r="H8" s="17" t="s"/>
-      <x:c r="I8" s="17" t="s"/>
-      <x:c r="J8" s="17" t="s"/>
-      <x:c r="K8" s="17" t="s"/>
-      <x:c r="L8" s="17" t="s"/>
-      <x:c r="M8" s="17" t="s"/>
+      <x:c r="B8" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45761.1071296296</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>45761.1071412037</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1459705</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45761.1243865741</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B9" s="9" t="s"/>
@@ -982,44 +1009,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="18" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="20" t="s"/>
-      <x:c r="F11" s="20" t="s"/>
+      <x:c r="B11" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s"/>
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="16" t="s"/>
+      <x:c r="F11" s="16" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="21" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="s">
-        <x:v>11</x:v>
+      <x:c r="B12" s="17" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C12" s="18" t="s"/>
+      <x:c r="D12" s="18" t="s"/>
+      <x:c r="E12" s="18" t="s"/>
+      <x:c r="F12" s="19" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="24" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="n">
+      <x:c r="B13" s="20" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="27" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="B14" s="23" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2123,18 +2150,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -2152,73 +2167,85 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s"/>
-      <x:c r="E6" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46078.1190856481</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46078.1190856481</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1516142</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>46078.3824768519</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s"/>
-      <x:c r="C7" s="16" t="s"/>
-      <x:c r="D7" s="16" t="s"/>
-      <x:c r="E7" s="16" t="s"/>
-      <x:c r="F7" s="16" t="s"/>
-      <x:c r="G7" s="16" t="s"/>
-      <x:c r="H7" s="16" t="s"/>
-      <x:c r="I7" s="16" t="s"/>
-      <x:c r="J7" s="16" t="s"/>
-      <x:c r="K7" s="16" t="s"/>
-      <x:c r="L7" s="16" t="s"/>
-      <x:c r="M7" s="16" t="s"/>
+      <x:c r="B7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="17" t="s"/>
-      <x:c r="C8" s="17" t="s"/>
-      <x:c r="D8" s="17" t="s"/>
-      <x:c r="E8" s="17" t="s"/>
-      <x:c r="F8" s="17" t="s"/>
-      <x:c r="G8" s="17" t="s"/>
-      <x:c r="H8" s="17" t="s"/>
-      <x:c r="I8" s="17" t="s"/>
-      <x:c r="J8" s="17" t="s"/>
-      <x:c r="K8" s="17" t="s"/>
-      <x:c r="L8" s="17" t="s"/>
-      <x:c r="M8" s="17" t="s"/>
+      <x:c r="B8" s="11" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s"/>
+      <x:c r="E8" s="11" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46078.1190856481</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>46078.1190856481</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1516142</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46078.3824768519</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B9" s="9" t="s"/>
@@ -2236,44 +2263,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="18" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="20" t="s"/>
-      <x:c r="F11" s="20" t="s"/>
+      <x:c r="B11" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s"/>
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="16" t="s"/>
+      <x:c r="F11" s="16" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="21" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="s">
-        <x:v>11</x:v>
+      <x:c r="B12" s="17" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C12" s="18" t="s"/>
+      <x:c r="D12" s="18" t="s"/>
+      <x:c r="E12" s="18" t="s"/>
+      <x:c r="F12" s="19" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="24" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="n">
+      <x:c r="B13" s="20" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="27" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="B14" s="23" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-KIM-LAWAN-evaluator-cache-serviceTracking-KIM-LAWAN-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-KIM-LAWAN-evaluator-cache-serviceTracking-KIM-LAWAN-XIII-202501-202612.xlsx
@@ -23,12 +23,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
   <x:si>
     <x:t>KIM LAWAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>XIII | April 2025</x:t>
   </x:si>
   <x:si>
     <x:t>Application Type</x:t>
@@ -100,6 +103,9 @@
     <x:t>TOTAL</x:t>
   </x:si>
   <x:si>
+    <x:t>XIII | February 2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>Amateur</x:t>
   </x:si>
   <x:si>
@@ -122,7 +128,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -162,6 +168,30 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="16"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -433,14 +463,23 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="23">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -453,56 +492,56 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="26">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -533,67 +572,79 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -822,58 +873,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -916,81 +967,81 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="G8" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>45761.1071296296</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="15">
         <x:v>45761.1071412037</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1459705</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>45761.1243865741</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -1009,44 +1060,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s"/>
-      <x:c r="D11" s="15" t="s"/>
-      <x:c r="E11" s="16" t="s"/>
-      <x:c r="F11" s="16" t="s"/>
+      <x:c r="B11" s="17" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="17" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C12" s="18" t="s"/>
-      <x:c r="D12" s="18" t="s"/>
-      <x:c r="E12" s="18" t="s"/>
-      <x:c r="F12" s="19" t="s">
+      <x:c r="B12" s="20" t="s">
         <x:v>23</x:v>
+      </x:c>
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="20" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="21" t="s"/>
-      <x:c r="F13" s="22" t="n">
+      <x:c r="B13" s="23" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="n">
+      <x:c r="B14" s="26" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2033,7 +2084,7 @@
   <x:mergeCells count="7">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
     <x:mergeCell ref="B13:E13"/>
@@ -2078,58 +2129,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -2172,79 +2223,79 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="s"/>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="F8" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>46078.1190856481</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="15">
         <x:v>46078.1190856481</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1516142</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>46078.3824768519</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -2263,44 +2314,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s"/>
-      <x:c r="D11" s="15" t="s"/>
-      <x:c r="E11" s="16" t="s"/>
-      <x:c r="F11" s="16" t="s"/>
+      <x:c r="B11" s="17" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="17" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C12" s="18" t="s"/>
-      <x:c r="D12" s="18" t="s"/>
-      <x:c r="E12" s="18" t="s"/>
-      <x:c r="F12" s="19" t="s">
+      <x:c r="B12" s="20" t="s">
         <x:v>23</x:v>
+      </x:c>
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="20" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="21" t="s"/>
-      <x:c r="F13" s="22" t="n">
+      <x:c r="B13" s="23" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="n">
+      <x:c r="B14" s="26" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -3287,7 +3338,7 @@
   <x:mergeCells count="7">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
     <x:mergeCell ref="B13:E13"/>

--- a/reports/service-tracking-report-KIM-LAWAN-evaluator-cache-serviceTracking-KIM-LAWAN-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-KIM-LAWAN-evaluator-cache-serviceTracking-KIM-LAWAN-XIII-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -68,6 +68,42 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ApplicationType}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Name}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Status}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Address}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.PermitNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ReferenceNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DateOfFiling}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ExpirationDate}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Amount}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DatePaid}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Restricted Radiotelephone Operator's Certificate for Land Mobile Station (NEW)</x:t>
@@ -125,10 +161,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
+    <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
+    <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="15">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -173,15 +211,7 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="16"/>
-      <x:color rgb="FF0000FF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF0000FF"/>
+      <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -197,15 +227,15 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -220,13 +250,6 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -463,26 +486,26 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -492,56 +515,59 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="29">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -572,79 +598,91 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -873,78 +911,90 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="28" customHeight="1">
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="10" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C1" s="10" t="s"/>
-      <x:c r="D1" s="10" t="s"/>
-      <x:c r="E1" s="10" t="s"/>
-      <x:c r="F1" s="10" t="s"/>
-      <x:c r="G1" s="10" t="s"/>
-      <x:c r="H1" s="10" t="s"/>
-      <x:c r="I1" s="10" t="s"/>
-      <x:c r="J1" s="10" t="s"/>
-      <x:c r="K1" s="10" t="s"/>
-      <x:c r="L1" s="10" t="s"/>
-      <x:c r="M1" s="10" t="s"/>
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="22" customHeight="1">
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="11" t="s"/>
-      <x:c r="D2" s="11" t="s"/>
-      <x:c r="E2" s="11" t="s"/>
-      <x:c r="F2" s="11" t="s"/>
-      <x:c r="G2" s="11" t="s"/>
-      <x:c r="H2" s="11" t="s"/>
-      <x:c r="I2" s="11" t="s"/>
-      <x:c r="J2" s="11" t="s"/>
-      <x:c r="K2" s="11" t="s"/>
-      <x:c r="L2" s="11" t="s"/>
-      <x:c r="M2" s="11" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28" ht="22" customHeight="1">
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="12" t="s"/>
-      <x:c r="D3" s="12" t="s"/>
-      <x:c r="E3" s="12" t="s"/>
-      <x:c r="F3" s="12" t="s"/>
-      <x:c r="G3" s="12" t="s"/>
-      <x:c r="H3" s="12" t="s"/>
-      <x:c r="I3" s="12" t="s"/>
-      <x:c r="J3" s="12" t="s"/>
-      <x:c r="K3" s="12" t="s"/>
-      <x:c r="L3" s="12" t="s"/>
-      <x:c r="M3" s="12" t="s"/>
+      <x:c r="B3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
-    <x:row r="4" spans="1:28">
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
       <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28">
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C5" s="12" t="s"/>
+      <x:c r="D5" s="12" t="s"/>
+      <x:c r="E5" s="12" t="s"/>
+      <x:c r="F5" s="12" t="s"/>
+      <x:c r="G5" s="12" t="s"/>
+      <x:c r="H5" s="12" t="s"/>
+      <x:c r="I5" s="12" t="s"/>
+      <x:c r="J5" s="12" t="s"/>
+      <x:c r="K5" s="12" t="s"/>
+      <x:c r="L5" s="12" t="s"/>
+      <x:c r="M5" s="12" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -965,7 +1015,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1005,104 +1055,141 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="9" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="C8" s="9" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="D8" s="9" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="E8" s="9" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="F8" s="9" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="G8" s="9" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="15">
+      <x:c r="H8" s="9" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K8" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L8" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="M8" s="9" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="14" t="s"/>
+      <x:c r="C9" s="14" t="s"/>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s"/>
+      <x:c r="F9" s="14" t="s"/>
+      <x:c r="G9" s="14" t="s"/>
+      <x:c r="H9" s="14" t="s"/>
+      <x:c r="I9" s="14" t="s"/>
+      <x:c r="J9" s="14" t="s"/>
+      <x:c r="K9" s="14" t="s"/>
+      <x:c r="L9" s="14" t="s"/>
+      <x:c r="M9" s="14" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
         <x:v>45761.1071296296</x:v>
       </x:c>
-      <x:c r="I8" s="15">
+      <x:c r="I10" s="17">
         <x:v>45761.1071412037</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
+      <x:c r="J10" s="16" t="n">
         <x:v>1459705</x:v>
       </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="L8" s="15">
+      <x:c r="L10" s="19">
         <x:v>45761.1243865741</x:v>
       </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="M10" s="15" t="s">
+        <x:v>33</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="20" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="22" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="s"/>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="19" t="s"/>
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="23" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="s">
+        <x:v>36</x:v>
+      </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="20" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="22" t="s">
-        <x:v>24</x:v>
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="26" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="n">
+    <x:row r="16" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B16" s="29" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C16" s="30" t="s"/>
+      <x:c r="D16" s="30" t="s"/>
+      <x:c r="E16" s="30" t="s"/>
+      <x:c r="F16" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="26" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2081,14 +2168,15 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="7">
-    <x:mergeCell ref="B1:M1"/>
-    <x:mergeCell ref="B2:M2"/>
+  <x:mergeCells count="8">
+    <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B11:F11"/>
-    <x:mergeCell ref="B12:E12"/>
-    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B13:F13"/>
     <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -2129,78 +2217,90 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="28" customHeight="1">
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="10" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C1" s="10" t="s"/>
-      <x:c r="D1" s="10" t="s"/>
-      <x:c r="E1" s="10" t="s"/>
-      <x:c r="F1" s="10" t="s"/>
-      <x:c r="G1" s="10" t="s"/>
-      <x:c r="H1" s="10" t="s"/>
-      <x:c r="I1" s="10" t="s"/>
-      <x:c r="J1" s="10" t="s"/>
-      <x:c r="K1" s="10" t="s"/>
-      <x:c r="L1" s="10" t="s"/>
-      <x:c r="M1" s="10" t="s"/>
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="22" customHeight="1">
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="11" t="s"/>
-      <x:c r="D2" s="11" t="s"/>
-      <x:c r="E2" s="11" t="s"/>
-      <x:c r="F2" s="11" t="s"/>
-      <x:c r="G2" s="11" t="s"/>
-      <x:c r="H2" s="11" t="s"/>
-      <x:c r="I2" s="11" t="s"/>
-      <x:c r="J2" s="11" t="s"/>
-      <x:c r="K2" s="11" t="s"/>
-      <x:c r="L2" s="11" t="s"/>
-      <x:c r="M2" s="11" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28" ht="22" customHeight="1">
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="12" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C3" s="12" t="s"/>
-      <x:c r="D3" s="12" t="s"/>
-      <x:c r="E3" s="12" t="s"/>
-      <x:c r="F3" s="12" t="s"/>
-      <x:c r="G3" s="12" t="s"/>
-      <x:c r="H3" s="12" t="s"/>
-      <x:c r="I3" s="12" t="s"/>
-      <x:c r="J3" s="12" t="s"/>
-      <x:c r="K3" s="12" t="s"/>
-      <x:c r="L3" s="12" t="s"/>
-      <x:c r="M3" s="12" t="s"/>
+      <x:c r="B3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
-    <x:row r="4" spans="1:28">
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
       <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28">
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C5" s="12" t="s"/>
+      <x:c r="D5" s="12" t="s"/>
+      <x:c r="E5" s="12" t="s"/>
+      <x:c r="F5" s="12" t="s"/>
+      <x:c r="G5" s="12" t="s"/>
+      <x:c r="H5" s="12" t="s"/>
+      <x:c r="I5" s="12" t="s"/>
+      <x:c r="J5" s="12" t="s"/>
+      <x:c r="K5" s="12" t="s"/>
+      <x:c r="L5" s="12" t="s"/>
+      <x:c r="M5" s="12" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -2221,7 +2321,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -2261,102 +2361,139 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s"/>
-      <x:c r="E8" s="14" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
+      <x:c r="B8" s="9" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C8" s="9" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D8" s="9" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="9" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F8" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G8" s="9" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H8" s="9" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K8" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L8" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="M8" s="9" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="14" t="s"/>
+      <x:c r="C9" s="14" t="s"/>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s"/>
+      <x:c r="F9" s="14" t="s"/>
+      <x:c r="G9" s="14" t="s"/>
+      <x:c r="H9" s="14" t="s"/>
+      <x:c r="I9" s="14" t="s"/>
+      <x:c r="J9" s="14" t="s"/>
+      <x:c r="K9" s="14" t="s"/>
+      <x:c r="L9" s="14" t="s"/>
+      <x:c r="M9" s="14" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s"/>
+      <x:c r="E10" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
         <x:v>46078.1190856481</x:v>
       </x:c>
-      <x:c r="I8" s="15">
+      <x:c r="I10" s="17">
         <x:v>46078.1190856481</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
+      <x:c r="J10" s="16" t="n">
         <x:v>1516142</x:v>
       </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L8" s="15">
+      <x:c r="L10" s="19">
         <x:v>46078.3824768519</x:v>
       </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="M10" s="15" t="s">
+        <x:v>33</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="20" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="22" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="s"/>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="19" t="s"/>
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="23" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="s">
+        <x:v>36</x:v>
+      </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="20" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="22" t="s">
-        <x:v>24</x:v>
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="26" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="n">
+    <x:row r="16" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B16" s="29" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C16" s="30" t="s"/>
+      <x:c r="D16" s="30" t="s"/>
+      <x:c r="E16" s="30" t="s"/>
+      <x:c r="F16" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="26" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3335,14 +3472,15 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="7">
-    <x:mergeCell ref="B1:M1"/>
-    <x:mergeCell ref="B2:M2"/>
+  <x:mergeCells count="8">
+    <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B11:F11"/>
-    <x:mergeCell ref="B12:E12"/>
-    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B13:F13"/>
     <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-KIM-LAWAN-evaluator-cache-serviceTracking-KIM-LAWAN-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-KIM-LAWAN-evaluator-cache-serviceTracking-KIM-LAWAN-XIII-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -68,42 +68,6 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ApplicationType}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Name}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Status}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Address}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.PermitNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ReferenceNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DateOfFiling}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ExpirationDate}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Amount}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DatePaid}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Restricted Radiotelephone Operator's Certificate for Land Mobile Station (NEW)</x:t>
@@ -166,7 +130,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -210,14 +174,6 @@
     <x:font>
       <x:b/>
       <x:vertAlign val="baseline"/>
-      <x:sz val="16"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
@@ -232,10 +188,18 @@
       <x:family val="2"/>
     </x:font>
     <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -250,6 +214,13 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -494,16 +465,16 @@
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -515,24 +486,21 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -551,10 +519,13 @@
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -567,7 +538,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -598,28 +569,20 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -634,10 +597,6 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -662,15 +621,15 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1015,7 +974,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1055,138 +1014,101 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="9" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="9" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="9" t="s">
+      <x:c r="H8" s="15">
+        <x:v>45761.1071296296</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>45761.1071412037</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1459705</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>45761.1243865741</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J8" s="9" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="K8" s="9" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="L8" s="9" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>26</x:v>
-      </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>45761.1071296296</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>45761.1071412037</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1459705</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>45761.1243865741</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="20" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="22" t="s"/>
+      <x:c r="B13" s="17" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C13" s="18" t="s"/>
+      <x:c r="D13" s="18" t="s"/>
+      <x:c r="E13" s="19" t="s"/>
+      <x:c r="F13" s="19" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="s">
-        <x:v>36</x:v>
+      <x:c r="B14" s="20" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C14" s="21" t="s"/>
+      <x:c r="D14" s="21" t="s"/>
+      <x:c r="E14" s="21" t="s"/>
+      <x:c r="F14" s="22" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
+      <x:c r="B15" s="23" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C15" s="24" t="s"/>
+      <x:c r="D15" s="24" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="29" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C16" s="30" t="s"/>
-      <x:c r="D16" s="30" t="s"/>
-      <x:c r="E16" s="30" t="s"/>
-      <x:c r="F16" s="31" t="n">
+      <x:c r="B16" s="26" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2288,7 +2210,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>38</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -2321,7 +2243,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -2361,136 +2283,99 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C8" s="9" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D8" s="9" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="9" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F8" s="9" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G8" s="9" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>46078.1190856481</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>46078.1190856481</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1516142</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>46078.3824768519</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J8" s="9" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="K8" s="9" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="L8" s="9" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>26</x:v>
-      </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="15" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>46078.1190856481</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>46078.1190856481</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1516142</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>46078.3824768519</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="20" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="22" t="s"/>
+      <x:c r="B13" s="17" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C13" s="18" t="s"/>
+      <x:c r="D13" s="18" t="s"/>
+      <x:c r="E13" s="19" t="s"/>
+      <x:c r="F13" s="19" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="s">
-        <x:v>36</x:v>
+      <x:c r="B14" s="20" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C14" s="21" t="s"/>
+      <x:c r="D14" s="21" t="s"/>
+      <x:c r="E14" s="21" t="s"/>
+      <x:c r="F14" s="22" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
+      <x:c r="B15" s="23" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C15" s="24" t="s"/>
+      <x:c r="D15" s="24" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="29" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C16" s="30" t="s"/>
-      <x:c r="D16" s="30" t="s"/>
-      <x:c r="E16" s="30" t="s"/>
-      <x:c r="F16" s="31" t="n">
+      <x:c r="B16" s="26" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-KIM-LAWAN-evaluator-cache-serviceTracking-KIM-LAWAN-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-KIM-LAWAN-evaluator-cache-serviceTracking-KIM-LAWAN-XIII-202501-202612.xlsx
@@ -1068,50 +1068,50 @@
       <x:c r="M9" s="9" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="17" t="s">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C13" s="18" t="s"/>
-      <x:c r="D13" s="18" t="s"/>
-      <x:c r="E13" s="19" t="s"/>
-      <x:c r="F13" s="19" t="s"/>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
     </x:row>
-    <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="20" t="s">
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C14" s="21" t="s"/>
-      <x:c r="D14" s="21" t="s"/>
-      <x:c r="E14" s="21" t="s"/>
-      <x:c r="F14" s="22" t="s">
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="23" t="s">
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="23" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="n">
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="26" t="s">
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2095,10 +2095,10 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B13:F13"/>
+    <x:mergeCell ref="B11:F11"/>
+    <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
     <x:mergeCell ref="B14:E14"/>
-    <x:mergeCell ref="B15:E15"/>
-    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -2335,50 +2335,50 @@
       <x:c r="M9" s="9" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="17" t="s">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C13" s="18" t="s"/>
-      <x:c r="D13" s="18" t="s"/>
-      <x:c r="E13" s="19" t="s"/>
-      <x:c r="F13" s="19" t="s"/>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
     </x:row>
-    <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="20" t="s">
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C14" s="21" t="s"/>
-      <x:c r="D14" s="21" t="s"/>
-      <x:c r="E14" s="21" t="s"/>
-      <x:c r="F14" s="22" t="s">
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="23" t="s">
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="23" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="n">
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="26" t="s">
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3362,10 +3362,10 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B13:F13"/>
+    <x:mergeCell ref="B11:F11"/>
+    <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
     <x:mergeCell ref="B14:E14"/>
-    <x:mergeCell ref="B15:E15"/>
-    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-KIM-LAWAN-evaluator-cache-serviceTracking-KIM-LAWAN-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-KIM-LAWAN-evaluator-cache-serviceTracking-KIM-LAWAN-XIII-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -88,6 +88,9 @@
     <x:t>61-4-2025-1001</x:t>
   </x:si>
   <x:si>
+    <x:t>1459705</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cherry Mae Anub</x:t>
   </x:si>
   <x:si>
@@ -119,6 +122,9 @@
   </x:si>
   <x:si>
     <x:t>70-2-2026-1038-895</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1516142</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1035,22 +1041,22 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H8" s="15">
-        <x:v>45761.1071296296</x:v>
+        <x:v>45761.1071346991</x:v>
       </x:c>
       <x:c r="I8" s="15">
-        <x:v>45761.1071412037</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1459705</x:v>
+        <x:v>45761.1071426852</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
       <x:c r="K8" s="16" t="n">
         <x:v>300</x:v>
       </x:c>
       <x:c r="L8" s="15">
-        <x:v>45761.1243865741</x:v>
+        <x:v>45761.1243943866</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -1070,7 +1076,7 @@
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="17" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C11" s="18" t="s"/>
       <x:c r="D11" s="18" t="s"/>
@@ -1079,13 +1085,13 @@
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
       <x:c r="B12" s="20" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C12" s="21" t="s"/>
       <x:c r="D12" s="21" t="s"/>
       <x:c r="E12" s="21" t="s"/>
       <x:c r="F12" s="22" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
@@ -1101,7 +1107,7 @@
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
       <x:c r="B14" s="26" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C14" s="27" t="s"/>
       <x:c r="D14" s="27" t="s"/>
@@ -2210,7 +2216,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -2286,38 +2292,38 @@
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D8" s="14" t="s"/>
       <x:c r="E8" s="14" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H8" s="15">
-        <x:v>46078.1190856481</x:v>
+        <x:v>46078.1190888079</x:v>
       </x:c>
       <x:c r="I8" s="15">
-        <x:v>46078.1190856481</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1516142</x:v>
+        <x:v>46078.1190892014</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="s">
+        <x:v>33</x:v>
       </x:c>
       <x:c r="K8" s="16" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="L8" s="15">
-        <x:v>46078.3824768519</x:v>
+        <x:v>46078.3824810995</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -2337,7 +2343,7 @@
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="17" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C11" s="18" t="s"/>
       <x:c r="D11" s="18" t="s"/>
@@ -2346,18 +2352,18 @@
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
       <x:c r="B12" s="20" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C12" s="21" t="s"/>
       <x:c r="D12" s="21" t="s"/>
       <x:c r="E12" s="21" t="s"/>
       <x:c r="F12" s="22" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
       <x:c r="B13" s="23" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C13" s="24" t="s"/>
       <x:c r="D13" s="24" t="s"/>
@@ -2368,7 +2374,7 @@
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
       <x:c r="B14" s="26" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C14" s="27" t="s"/>
       <x:c r="D14" s="27" t="s"/>

--- a/reports/service-tracking-report-KIM-LAWAN-evaluator-cache-serviceTracking-KIM-LAWAN-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-KIM-LAWAN-evaluator-cache-serviceTracking-KIM-LAWAN-XIII-202501-202612.xlsx
@@ -980,7 +980,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1020,7 +1020,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
@@ -2249,7 +2249,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -2289,7 +2289,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>28</x:v>

--- a/reports/service-tracking-report-KIM-LAWAN-evaluator-cache-serviceTracking-KIM-LAWAN-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-KIM-LAWAN-evaluator-cache-serviceTracking-KIM-LAWAN-XIII-202501-202612.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <x:si>
-    <x:t>EVALUATOR SUMMARY</x:t>
+    <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
   <x:si>
     <x:t>KIM LAWAN</x:t>

--- a/reports/service-tracking-report-KIM-LAWAN-evaluator-cache-serviceTracking-KIM-LAWAN-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-KIM-LAWAN-evaluator-cache-serviceTracking-KIM-LAWAN-XIII-202501-202612.xlsx
@@ -23,15 +23,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
   <x:si>
     <x:t>KIM LAWAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>XIII | April 2025</x:t>
   </x:si>
   <x:si>
     <x:t>Application Type</x:t>
@@ -104,9 +101,6 @@
   </x:si>
   <x:si>
     <x:t>TOTAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>XIII | February 2026</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur</x:t>
@@ -463,7 +457,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="27">
+  <x:cellStyleXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -480,6 +474,9 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -544,7 +541,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="29">
+  <x:cellXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -580,6 +577,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -946,20 +947,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45748</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -982,81 +983,81 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="E8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="F8" s="15" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="G8" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="H8" s="16">
+        <x:v>45761.1071346991</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>45761.1071426852</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45761.1071346991</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>45761.1071426852</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="s">
+      <x:c r="K8" s="17" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="L8" s="16">
+        <x:v>45761.1243943866</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45761.1243943866</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -1075,44 +1076,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="s"/>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="19" t="s"/>
+      <x:c r="B11" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C11" s="19" t="s"/>
+      <x:c r="D11" s="19" t="s"/>
+      <x:c r="E11" s="20" t="s"/>
+      <x:c r="F11" s="20" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="20" t="s">
+      <x:c r="B12" s="21" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="23" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="22" t="s">
-        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="n">
+      <x:c r="B13" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="26" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
+      <x:c r="B14" s="27" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2215,20 +2216,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46054</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -2251,79 +2252,79 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s"/>
+      <x:c r="E8" s="15" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="F8" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s"/>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="G8" s="15" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="H8" s="16">
+        <x:v>46078.1190888079</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>46078.1190892014</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>46078.1190888079</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>46078.1190892014</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L8" s="15">
+      <x:c r="L8" s="16">
         <x:v>46078.3824810995</x:v>
       </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M8" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -2342,44 +2343,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="s"/>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="19" t="s"/>
+      <x:c r="B11" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C11" s="19" t="s"/>
+      <x:c r="D11" s="19" t="s"/>
+      <x:c r="E11" s="20" t="s"/>
+      <x:c r="F11" s="20" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="20" t="s">
+      <x:c r="B12" s="21" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="23" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="22" t="s">
-        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="n">
+      <x:c r="B13" s="24" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="26" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
+      <x:c r="B14" s="27" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-KIM-LAWAN-evaluator-cache-serviceTracking-KIM-LAWAN-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-KIM-LAWAN-evaluator-cache-serviceTracking-KIM-LAWAN-XIII-202501-202612.xlsx
@@ -130,7 +130,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -170,14 +170,6 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -457,7 +449,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="28">
+  <x:cellStyleXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -468,16 +460,13 @@
     <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -489,59 +478,59 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="30">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -576,79 +565,75 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -950,17 +935,17 @@
       <x:c r="B5" s="12">
         <x:v>45748</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -983,80 +968,80 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="16">
+      <x:c r="H8" s="15">
         <x:v>45761.1071346991</x:v>
       </x:c>
-      <x:c r="I8" s="16">
+      <x:c r="I8" s="15">
         <x:v>45761.1071426852</x:v>
       </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="J8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="L8" s="16">
+      <x:c r="L8" s="15">
         <x:v>45761.1243943866</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -1076,44 +1061,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="18" t="s">
+      <x:c r="B11" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="20" t="s"/>
-      <x:c r="F11" s="20" t="s"/>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="21" t="s">
+      <x:c r="B12" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="s">
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="24" t="s">
+      <x:c r="B13" s="23" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="n">
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="27" t="s">
+      <x:c r="B14" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2219,17 +2204,17 @@
       <x:c r="B5" s="12">
         <x:v>46054</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -2252,78 +2237,78 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s"/>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="H8" s="16">
+      <x:c r="H8" s="15">
         <x:v>46078.1190888079</x:v>
       </x:c>
-      <x:c r="I8" s="16">
+      <x:c r="I8" s="15">
         <x:v>46078.1190892014</x:v>
       </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="J8" s="14" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L8" s="16">
+      <x:c r="L8" s="15">
         <x:v>46078.3824810995</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -2343,44 +2328,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="18" t="s">
+      <x:c r="B11" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="20" t="s"/>
-      <x:c r="F11" s="20" t="s"/>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="21" t="s">
+      <x:c r="B12" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="s">
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="24" t="s">
+      <x:c r="B13" s="23" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="n">
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="27" t="s">
+      <x:c r="B14" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
